--- a/news_daily/2026-08-19.xlsx
+++ b/news_daily/2026-08-19.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1011,180 +1027,212 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T20:49:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Uber Eats to pay $4.4 million in settlement with Seattle</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>'-0.153</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNU1ZHd2REVWpfSmZJYndGeG9ZdEZqOTBXeWFldk9wR0VISl9UakFSZG1Da1ZOOExOaGpPS0FGQ0VSUVU4Ykl4RS0xRHBrUVBMUXJ5c19GdEI0bEFBZmd0ZXY3SHl3WU9JYzB6cmVDbzM2Vjh2aklBWDNCc1dod056RFZXR0h6NUV3ZWhuUGV6X2RZR1EtSm5QdFBqZmF0YnZydFc3STV5d0tMdzRVY2FzV0E5YlRvUEtVejFQV0Z4RGRrOXJjdkRfc0dmNmVEbUU?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>KING5.com</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>c85efedced3b4839a63f8909d9a70e78</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>e3ae4218f43aa7d1c1c96230</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>c2138061cc9061a94eceeb80</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.153</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNU1ZHd2REVWpfSmZJYndGeG9ZdEZqOTBXeWFldk9wR0VISl9UakFSZG1Da1ZOOExOaGpPS0FGQ0VSUVU4Ykl4RS0xRHBrUVBMUXJ5c19GdEI0bEFBZmd0ZXY3SHl3WU9JYzB6cmVDbzM2Vjh2aklBWDNCc1dod056RFZXR0h6NUV3ZWhuUGV6X2RZR1EtSm5QdFBqZmF0YnZydFc3STV5d0tMdzRVY2FzV0E5YlRvUEtVejFQV0Z4RGRrOXJjdkRfc0dmNmVEbUU?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>KING5.com</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>e3ae4218f43aa7d1c1c96230</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>c2138061cc9061a94eceeb80</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1351,6 +1399,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1525,180 +1577,212 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Uber Eats to pay $4.4M settlement to Seattle delivery workers</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.068</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOcktMQkF1LWpaOGpjbFF1THR4RjdKTnRMemk0amtsZkF1SllvLURBUVJUQmEzdUdNb0t0UEFiWk91Z3RoQUM2aXJxOFoya2VQeGNvYVdfUWd4TUExNVVickNQZDZLdlQ0VHlsSGhHQVNOTkFTSFVTeFAyVlpzTTJHMmNfQm8wX0l0eFRZeWh4dGF2d1ctc2NMMm0zcmtWNEsx?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>The Seattle Times</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>6a194c3b8b124e63ab06a9afbc48030c</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>c3662f43859f4dcaa583c829</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>c2aed1e8bbb3ec85393b7f6b</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOcktMQkF1LWpaOGpjbFF1THR4RjdKTnRMemk0amtsZkF1SllvLURBUVJUQmEzdUdNb0t0UEFiWk91Z3RoQUM2aXJxOFoya2VQeGNvYVdfUWd4TUExNVVickNQZDZLdlQ0VHlsSGhHQVNOTkFTSFVTeFAyVlpzTTJHMmNfQm8wX0l0eFRZeWh4dGF2d1ctc2NMMm0zcmtWNEsx?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The Seattle Times</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>c3662f43859f4dcaa583c829</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>c2aed1e8bbb3ec85393b7f6b</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1857,6 +1941,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2031,6 +2119,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2205,6 +2297,10 @@
       </c>
       <c r="BG9" s="2" t="inlineStr"/>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2363,6 +2459,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2413,13 +2513,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2472,7 +2576,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>6b5210420d254008bfcba4c04153c24e</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>55cbe191667d856758c5db3e</t>
@@ -2493,7 +2601,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2537,6 +2649,18 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2703,6 +2827,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2877,6 +3005,10 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3043,6 +3175,10 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr"/>
+      <c r="BL14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3217,6 +3353,10 @@
         </is>
       </c>
       <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BI15" s="4" t="inlineStr"/>
+      <c r="BJ15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr"/>
+      <c r="BL15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3391,6 +3531,10 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3431,7 +3575,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3441,13 +3585,17 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3487,7 +3635,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -3500,7 +3648,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>24d8747c26e34ed6881ad42db25cf75b</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>7d8a1737e4a003eb3c6d6ed7</t>
@@ -3521,7 +3673,11 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr"/>
       <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="3" t="inlineStr"/>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
@@ -3565,6 +3721,22 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3731,172 +3903,204 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr"/>
+      <c r="BL18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>2026-08-19T06:23:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Coinbase Must Face Investor Suit Over SEC, Bankruptcy Risks</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>'-0.89</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>011ea57ee19345e6a830245c47ce9892</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>98220bbfad4ca2dced3d8acb</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>8797dd1de30c63f33cb927ef</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>'-0.89</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="5" t="inlineStr"/>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr"/>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z19" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="5" t="inlineStr"/>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>98220bbfad4ca2dced3d8acb</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>8797dd1de30c63f33cb927ef</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr"/>
-      <c r="AF19" s="5" t="inlineStr"/>
-      <c r="AG19" s="5" t="inlineStr"/>
-      <c r="AH19" s="5" t="inlineStr"/>
-      <c r="AI19" s="5" t="inlineStr"/>
-      <c r="AJ19" s="5" t="inlineStr"/>
-      <c r="AK19" s="5" t="inlineStr"/>
-      <c r="AL19" s="5" t="inlineStr"/>
-      <c r="AM19" s="5" t="inlineStr"/>
-      <c r="AN19" s="5" t="inlineStr"/>
-      <c r="AO19" s="5" t="inlineStr"/>
-      <c r="AP19" s="5" t="inlineStr"/>
-      <c r="AQ19" s="5" t="inlineStr"/>
-      <c r="AR19" s="5" t="inlineStr"/>
-      <c r="AS19" s="5" t="inlineStr"/>
-      <c r="AT19" s="5" t="inlineStr"/>
-      <c r="AU19" s="5" t="inlineStr"/>
-      <c r="AV19" s="5" t="inlineStr"/>
-      <c r="AW19" s="5" t="inlineStr"/>
-      <c r="AX19" s="5" t="inlineStr"/>
-      <c r="AY19" s="5" t="inlineStr"/>
-      <c r="AZ19" s="5" t="inlineStr"/>
-      <c r="BA19" s="5" t="inlineStr"/>
-      <c r="BB19" s="5" t="inlineStr">
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr"/>
+      <c r="AX19" s="3" t="inlineStr"/>
+      <c r="AY19" s="3" t="inlineStr"/>
+      <c r="AZ19" s="3" t="inlineStr"/>
+      <c r="BA19" s="3" t="inlineStr"/>
+      <c r="BB19" s="3" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC19" s="5" t="inlineStr">
+      <c r="BC19" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="5" t="inlineStr"/>
-      <c r="BE19" s="5" t="inlineStr">
+      <c r="BD19" s="3" t="inlineStr"/>
+      <c r="BE19" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="5" t="inlineStr"/>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BF19" s="3" t="inlineStr"/>
+      <c r="BG19" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="5" t="inlineStr"/>
+      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3943,17 +4147,17 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4006,7 +4210,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>c13f3ab3dc9a4caa9d5909c34cc0713d</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>723cdefc6cf396563b2b1ad0</t>
@@ -4029,7 +4237,7 @@
       <c r="AN20" s="3" t="inlineStr"/>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr"/>
@@ -4071,9 +4279,21 @@
       </c>
       <c r="BG20" s="3" t="inlineStr"/>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4084,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4147,6 +4367,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4450,6 +4674,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -4464,22 +4708,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T20:49:00+08:00</t>
+          <t>2026-08-19T15:00:00+08:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Uber Eats to pay $4.4 million in settlement with Seattle</t>
+          <t>As Meta faces trial for hooking kids on social media, NC's attorney general offers parents advice</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -4490,7 +4734,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -4500,13 +4744,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -4516,7 +4764,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>'-0.153</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -4530,12 +4778,12 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNU1ZHd2REVWpfSmZJYndGeG9ZdEZqOTBXeWFldk9wR0VISl9UakFSZG1Da1ZOOExOaGpPS0FGQ0VSUVU4Ykl4RS0xRHBrUVBMUXJ5c19GdEI0bEFBZmd0ZXY3SHl3WU9JYzB6cmVDbzM2Vjh2aklBWDNCc1dod056RFZXR0h6NUV3ZWhuUGV6X2RZR1EtSm5QdFBqZmF0YnZydFc3STV5d0tMdzRVY2FzV0E5YlRvUEtVejFQV0Z4RGRrOXJjdkRfc0dmNmVEbUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQX3VCSTR5X3V0N09Va1ZZWmNETkFiMkhGQWhFemF1MWhadUhxRW9Ed00zdlV2cGNUZng5c2U0azU5bmM3c0UtQThpaHk5UHlublZqRTBzVmhNa1dMMjU5NU5EemxlZWRfOHo3U2tTVG1YQlh4X2swZ2dNZjNjcXlzNE5VTUpHaXU0Y1VoM3cyNDlkVlpQLWtOaExGamVOY0RvVXI5dzZpa0VySjJEUjVKRmwwZUEyLVdlR2g4eE94LWZfc1dPaTVMVGxR?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>KING5.com</t>
+          <t>NC Newsline</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
@@ -4546,12 +4794,12 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>attorney general</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -4559,15 +4807,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>6b5210420d254008bfcba4c04153c24e</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>e3ae4218f43aa7d1c1c96230</t>
+          <t>55cbe191667d856758c5db3e</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>c2138061cc9061a94eceeb80</t>
+          <t>9100ec78b6e606f865f3b807</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -4580,7 +4832,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -4590,7 +4846,7 @@
       <c r="AV2" s="3" t="inlineStr"/>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX2" s="3" t="inlineStr"/>
@@ -4599,7 +4855,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -4610,534 +4866,582 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG2" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2026-08-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Uber Eats to pay $4.4M settlement to Seattle delivery workers</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>EA devs feel "the threat of layoffs at all times," especially after Saudi Arabia acquisition: "It's hard to see how teams or games that underperform wouldn't be dissolved"</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.945</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOcktMQkF1LWpaOGpjbFF1THR4RjdKTnRMemk0amtsZkF1SllvLURBUVJUQmEzdUdNb0t0UEFiWk91Z3RoQUM2aXJxOFoya2VQeGNvYVdfUWd4TUExNVVickNQZDZLdlQ0VHlsSGhHQVNOTkFTSFVTeFAyVlpzTTJHMmNfQm8wX0l0eFRZeWh4dGF2d1ctc2NMMm0zcmtWNEsx?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>The Seattle Times</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPb1I2bm4zelljeVc1ckotVzMtTHhwQmlzLW53VGhPc041cGxvdGFEeVdaWExWMEw0MHJSYy1xQjRPUERMS0ZHRW5qN1NRVFJhdy02Y1R1TVRlWk43YW1QNFN6WWs2R25yc3pQcC1fRXZRWGVRbTRNMUZlT184OVpveUdZTFJTNjZ5Rk9NYWp2RzFOVHVNbVAw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>c3662f43859f4dcaa583c829</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>c2aed1e8bbb3ec85393b7f6b</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>2df15df5265c5dd85d3cc96f</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>f2d43c051b02f6d0e68cd5d6</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr"/>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr"/>
+      <c r="BG3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Lennar Corporation Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-08-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>As Meta faces trial for hooking kids on social media, NC's attorney general offers parents advice</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>News - Lennar Mortgage data breach exposes personal information of more than 60,000 Texans</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.048</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQX3VCSTR5X3V0N09Va1ZZWmNETkFiMkhGQWhFemF1MWhadUhxRW9Ed00zdlV2cGNUZng5c2U0azU5bmM3c0UtQThpaHk5UHlublZqRTBzVmhNa1dMMjU5NU5EemxlZWRfOHo3U2tTVG1YQlh4X2swZ2dNZjNjcXlzNE5VTUpHaXU0Y1VoM3cyNDlkVlpQLWtOaExGamVOY0RvVXI5dzZpa0VySjJEUjVKRmwwZUEyLVdlR2g4eE94LWZfc1dPaTVMVGxR?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>NC Newsline</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.926</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdnZYOWhLcUdOcjdDXzFRenZYa1pfNy1ySDFHRlZ2OXJtSUFaMlo1bEZkS2M5QklBWURYNVRyZDJmZy1ETnViZm5reFR6WFJDT1A3TVVuMEhiUVlOeFA5TlFWLVV4RjcxVXRnamlsdFpxT19QWnJZSzRrOXdEQUQtTWlJOGQ1MGMxMGNvWFNzZlpYUWVSUVJON3UtOWRyeHVmRlNSMXVMLVBISDk4eEdWbGp6OWM3X0VD?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>teiss</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>55cbe191667d856758c5db3e</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>9100ec78b6e606f865f3b807</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>d6fe9154050795237fedcbbd</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>98248d8bb5062e16bbdce959</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>EA devs feel "the threat of layoffs at all times," especially after Saudi Arabia acquisition: "It's hard to see how teams or games that underperform wouldn't be dissolved"</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19T08:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Equifax Settlement Could Pay 4 Million Consumers Up to $280</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXNkT3lScldaMWk1bVNKX2xiaFhwNkxWYjd6ZG5kVWJMU3FIWDRlUTlEMFhPdnVhMk1MSkpudlRhaHVuRlZVNENOV2FFR3daMTdNcDFwSTBIbXZrZW0tMlVBcldXME5oQVhZRkc5Rk1Ub3hYZUl0c0pEeXZsTjN4dmJlRDFsbWdUU1hUbThVMERySzkyX3ZGc2wxUFlYSzjSAaQBQVVfeXFMTURITENfbWxtQlZycVVZNnhwLTVMM3hfZGR2VF9lLXZFMUVzQ0xtZXUtVnM2RWtBeUhxWFN6TlB6VUlCb2NPZXNtdldId3Zsb3BkWm1ZaVhXSjNESWdOaDduLTlZR1BZWGdteW9MQXlYYTVLaXZJanc4Rms4T2MxQVNVdDU5ZHh4MEpvMjJrSkw5WERjOFptR2tXbG9nTVlIa01rV1c?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>BadCredit.org</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>24d8747c26e34ed6881ad42db25cf75b</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>7d8a1737e4a003eb3c6d6ed7</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>fb248b9530e660b4d5037ed8</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>'-0.945</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPb1I2bm4zelljeVc1ckotVzMtTHhwQmlzLW53VGhPc041cGxvdGFEeVdaWExWMEw0MHJSYy1xQjRPUERMS0ZHRW5qN1NRVFJhdy02Y1R1TVRlWk43YW1QNFN6WWs2R25yc3pQcC1fRXZRWGVRbTRNMUZlT184OVpveUdZTFJTNjZ5Rk9NYWp2RzFOVHVNbVAw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>2df15df5265c5dd85d3cc96f</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>f2d43c051b02f6d0e68cd5d6</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -5152,22 +5456,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Lennar Corporation Class A Common Stock</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19T15:00:00+08:00</t>
+          <t>2026-08-19T06:42:47+08:00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>News - Lennar Mortgage data breach exposes personal information of more than 60,000 Texans</t>
+          <t>Eversource (ES) Financial Update: EPS Misses Its Estimate under the Current Snapshot; Session Reaction: The Stock Ends Up 0.43% at the Close - Quarterly Earnings Report</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -5178,7 +5482,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>財報不如預期</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -5204,7 +5508,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>'-0.926</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -5213,33 +5517,33 @@
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>原始代號與公司名稱交叉核對</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdnZYOWhLcUdOcjdDXzFRenZYa1pfNy1ySDFHRlZ2OXJtSUFaMlo1bEZkS2M5QklBWURYNVRyZDJmZy1ETnViZm5reFR6WFJDT1A3TVVuMEhiUVlOeFA5TlFWLVV4RjcxVXRnamlsdFpxT19QWnJZSzRrOXdEQUQtTWlJOGQ1MGMxMGNvWFNzZlpYUWVSUVJON3UtOWRyeHVmRlNSMXVMLVBISDk4eEdWbGp6OWM3X0VD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPdEFVMDRjMEhVSUNmTkt4b212bkw3cmpRY0NOMG5HTjh6U0VWZnBXNmtnS1hkdjJURGVjUTBCNHI1aUo0WjVrTW5tdms2VWFyX1lxS3JxV21ldGI3Y1M0LVpyeFIwUTRvT3cwU3dqQm1TZm9pR3FOcGdaNk9PLW9VaWYwVHRHQ3lpakhKLVFnWXZKSzcyUVpEaHctenVHdWo2VXU5SUJldWNidUJqOENqMDFCTGt2YlFVR0t5T3V3YU5leTAtX0hiX1l6TGhXb2Y2RnhTREhQcTlMR1diZ2QtQzlkSHhkR3ZXNjJtNUJaZm5qdW5HUDg2bmEwZUc5UjZVR2E1ZHVR?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>teiss</t>
+          <t>vinanet.vn</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>EARNINGS_MISS</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>EPS miss</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr">
@@ -5250,12 +5554,12 @@
       <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>d6fe9154050795237fedcbbd</t>
+          <t>855b6643ce59f8ffa91338ca</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>98248d8bb5062e16bbdce959</t>
+          <t>0f01c7d4a0fd1ba5bfe6dd13</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -5276,18 +5580,14 @@
       <c r="AT6" s="4" t="inlineStr"/>
       <c r="AU6" s="4" t="inlineStr"/>
       <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW6" s="4" t="inlineStr"/>
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr"/>
       <c r="AZ6" s="4" t="inlineStr"/>
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -5298,20 +5598,20 @@
       <c r="BD6" s="4" t="inlineStr"/>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
       <c r="BG6" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -5326,22 +5626,22 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T08:00:00+08:00</t>
+          <t>2026-08-19T06:23:00+08:00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Equifax Settlement Could Pay 4 Million Consumers Up to $280</t>
+          <t>Coinbase Must Face Investor Suit Over SEC, Bankruptcy Risks</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -5352,7 +5652,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -5362,13 +5662,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -5378,7 +5682,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>'-0.89</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
@@ -5392,28 +5696,28 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXNkT3lScldaMWk1bVNKX2xiaFhwNkxWYjd6ZG5kVWJMU3FIWDRlUTlEMFhPdnVhMk1MSkpudlRhaHVuRlZVNENOV2FFR3daMTdNcDFwSTBIbXZrZW0tMlVBcldXME5oQVhZRkc5Rk1Ub3hYZUl0c0pEeXZsTjN4dmJlRDFsbWdUU1hUbThVMERySzkyX3ZGc2wxUFlYSzjSAaQBQVVfeXFMTURITENfbWxtQlZycVVZNnhwLTVMM3hfZGR2VF9lLXZFMUVzQ0xtZXUtVnM2RWtBeUhxWFN6TlB6VUlCb2NPZXNtdldId3Zsb3BkWm1ZaVhXSjNESWdOaDduLTlZR1BZWGdteW9MQXlYYTVLaXZJanc4Rms4T2MxQVNVdDU5ZHh4MEpvMjJrSkw5WERjOFptR2tXbG9nTVlIa01rV1c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>BadCredit.org</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>bankruptcy</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -5421,15 +5725,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>011ea57ee19345e6a830245c47ce9892</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>7d8a1737e4a003eb3c6d6ed7</t>
+          <t>98220bbfad4ca2dced3d8acb</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>fb248b9530e660b4d5037ed8</t>
+          <t>8797dd1de30c63f33cb927ef</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr"/>
@@ -5442,7 +5750,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -5450,18 +5762,14 @@
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
       <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW7" s="3" t="inlineStr"/>
       <c r="AX7" s="3" t="inlineStr"/>
       <c r="AY7" s="3" t="inlineStr"/>
       <c r="AZ7" s="3" t="inlineStr"/>
       <c r="BA7" s="3" t="inlineStr"/>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="BC7" s="3" t="inlineStr">
@@ -5472,529 +5780,225 @@
       <c r="BD7" s="3" t="inlineStr"/>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="3" t="inlineStr"/>
       <c r="BG7" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Eversource Energy</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19T06:42:47+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Eversource (ES) Financial Update: EPS Misses Its Estimate under the Current Snapshot; Session Reaction: The Stock Ends Up 0.43% at the Close - Quarterly Earnings Report</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>AppLovin</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:19:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Apple Changes App Store Terms to Resolve E.U. Antitrust Dispute</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>'-0.39</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUDdna2V3bXFlOERIUnFkejQ5WkVBc2I3cVRoZXNGdWZDQnRMeUVEZ2x6VnVVbTJQenY4aDIwU0RLQ1JOMWVLazZmZ3N1MjVmLXFyc08xOWhBT0pLU1JDUzctczNpQmdkd1BuUHo0M1N3M3ZoNFktQmg4V2NOWjFwM2dxWngzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Barron's</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>c13f3ab3dc9a4caa9d5909c34cc0713d</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>723cdefc6cf396563b2b1ad0</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>ee5754561338bdfca7341bae</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0.322</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPdEFVMDRjMEhVSUNmTkt4b212bkw3cmpRY0NOMG5HTjh6U0VWZnBXNmtnS1hkdjJURGVjUTBCNHI1aUo0WjVrTW5tdms2VWFyX1lxS3JxV21ldGI3Y1M0LVpyeFIwUTRvT3cwU3dqQm1TZm9pR3FOcGdaNk9PLW9VaWYwVHRHQ3lpakhKLVFnWXZKSzcyUVpEaHctenVHdWo2VXU5SUJldWNidUJqOENqMDFCTGt2YlFVR0t5T3V3YU5leTAtX0hiX1l6TGhXb2Y2RnhTREhQcTlMR1diZ2QtQzlkSHhkR3ZXNjJtNUJaZm5qdW5HUDg2bmEwZUc5UjZVR2E1ZHVR?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>vinanet.vn</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>EPS miss</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>855b6643ce59f8ffa91338ca</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>0f01c7d4a0fd1ba5bfe6dd13</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr"/>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-19T06:23:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Coinbase Must Face Investor Suit Over SEC, Bankruptcy Risks</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>'-0.89</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA9" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr">
-        <is>
-          <t>98220bbfad4ca2dced3d8acb</t>
-        </is>
-      </c>
-      <c r="AD9" s="5" t="inlineStr">
-        <is>
-          <t>8797dd1de30c63f33cb927ef</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr"/>
-      <c r="AF9" s="5" t="inlineStr"/>
-      <c r="AG9" s="5" t="inlineStr"/>
-      <c r="AH9" s="5" t="inlineStr"/>
-      <c r="AI9" s="5" t="inlineStr"/>
-      <c r="AJ9" s="5" t="inlineStr"/>
-      <c r="AK9" s="5" t="inlineStr"/>
-      <c r="AL9" s="5" t="inlineStr"/>
-      <c r="AM9" s="5" t="inlineStr"/>
-      <c r="AN9" s="5" t="inlineStr"/>
-      <c r="AO9" s="5" t="inlineStr"/>
-      <c r="AP9" s="5" t="inlineStr"/>
-      <c r="AQ9" s="5" t="inlineStr"/>
-      <c r="AR9" s="5" t="inlineStr"/>
-      <c r="AS9" s="5" t="inlineStr"/>
-      <c r="AT9" s="5" t="inlineStr"/>
-      <c r="AU9" s="5" t="inlineStr"/>
-      <c r="AV9" s="5" t="inlineStr"/>
-      <c r="AW9" s="5" t="inlineStr"/>
-      <c r="AX9" s="5" t="inlineStr"/>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
-      <c r="BB9" s="5" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC9" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="5" t="inlineStr"/>
-      <c r="BE9" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="5" t="inlineStr"/>
-      <c r="BG9" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>AppLovin</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19T02:19:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Apple Changes App Store Terms to Resolve E.U. Antitrust Dispute</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.39</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUDdna2V3bXFlOERIUnFkejQ5WkVBc2I3cVRoZXNGdWZDQnRMeUVEZ2x6VnVVbTJQenY4aDIwU0RLQ1JOMWVLazZmZ3N1MjVmLXFyc08xOWhBT0pLU1JDUzctczNpQmdkd1BuUHo0M1N3M3ZoNFktQmg4V2NOWjFwM2dxWngzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Barron's</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>723cdefc6cf396563b2b1ad0</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>ee5754561338bdfca7341bae</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="BD8" s="3" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BE8" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr"/>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6005,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6068,6 +6072,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6369,6 +6377,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -6545,183 +6573,13 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>AppLovin</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19T02:19:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Apple Changes App Store Terms to Resolve E.U. Antitrust Dispute</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.39</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUDdna2V3bXFlOERIUnFkejQ5WkVBc2I3cVRoZXNGdWZDQnRMeUVEZ2x6VnVVbTJQenY4aDIwU0RLQ1JOMWVLazZmZ3N1MjVmLXFyc08xOWhBT0pLU1JDUzctczNpQmdkd1BuUHo0M1N3M3ZoNFktQmg4V2NOWjFwM2dxWngzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Barron's</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>723cdefc6cf396563b2b1ad0</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>ee5754561338bdfca7341bae</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6732,7 +6590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6795,6 +6653,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7098,9 +6960,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7111,7 +6993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7161,134 +7043,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7298,46 +7180,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7346,12 +7262,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7361,90 +7277,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7454,94 +7374,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7549,89 +7469,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-19.xlsx
+++ b/news_daily/2026-08-19.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -2154,32 +2154,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2232,7 +2232,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>c0e66e8b9074499e8191c719c456e74c</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>4c6e285d6eb5907045fb1fbf</t>
@@ -2255,7 +2259,7 @@
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP9" s="2" t="inlineStr"/>
@@ -2297,10 +2301,22 @@
       </c>
       <c r="BG9" s="2" t="inlineStr"/>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3011,174 +3027,198 @@
       <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Electronic Arts</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>EA devs feel "the threat of layoffs at all times," especially after Saudi Arabia acquisition: "It's hard to see how teams or games that underperform wouldn't be dissolved"</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>'-0.945</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPb1I2bm4zelljeVc1ckotVzMtTHhwQmlzLW53VGhPc041cGxvdGFEeVdaWExWMEw0MHJSYy1xQjRPUERMS0ZHRW5qN1NRVFJhdy02Y1R1TVRlWk43YW1QNFN6WWs2R25yc3pQcC1fRXZRWGVRbTRNMUZlT184OVpveUdZTFJTNjZ5Rk9NYWp2RzFOVHVNbVAw?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>b3ed2f7f2c1244a0901049bec55b0e44</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2df15df5265c5dd85d3cc96f</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>f2d43c051b02f6d0e68cd5d6</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.945</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPb1I2bm4zelljeVc1ckotVzMtTHhwQmlzLW53VGhPc041cGxvdGFEeVdaWExWMEw0MHJSYy1xQjRPUERMS0ZHRW5qN1NRVFJhdy02Y1R1TVRlWk43YW1QNFN6WWs2R25yc3pQcC1fRXZRWGVRbTRNMUZlT184OVpveUdZTFJTNjZ5Rk9NYWp2RzFOVHVNbVAw?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>2df15df5265c5dd85d3cc96f</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>f2d43c051b02f6d0e68cd5d6</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr"/>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="BC14" s="4" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF14" s="4" t="inlineStr"/>
-      <c r="BG14" s="4" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr"/>
-      <c r="BL14" s="4" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3229,13 +3269,17 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -3288,7 +3332,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>a6033bd01de44f7d8ee262f2e080fada</t>
+        </is>
+      </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
           <t>d6fe9154050795237fedcbbd</t>
@@ -3309,7 +3357,11 @@
       <c r="AL15" s="4" t="inlineStr"/>
       <c r="AM15" s="4" t="inlineStr"/>
       <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="4" t="inlineStr"/>
       <c r="AQ15" s="4" t="inlineStr"/>
       <c r="AR15" s="4" t="inlineStr"/>
@@ -3355,8 +3407,16 @@
       <c r="BH15" s="4" t="inlineStr"/>
       <c r="BI15" s="4" t="inlineStr"/>
       <c r="BJ15" s="4" t="inlineStr"/>
-      <c r="BK15" s="4" t="inlineStr"/>
-      <c r="BL15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3739,174 +3799,198 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Eversource Energy</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T06:42:47+08:00</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Eversource (ES) Financial Update: EPS Misses Its Estimate under the Current Snapshot; Session Reaction: The Stock Ends Up 0.43% at the Close - Quarterly Earnings Report</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.322</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPdEFVMDRjMEhVSUNmTkt4b212bkw3cmpRY0NOMG5HTjh6U0VWZnBXNmtnS1hkdjJURGVjUTBCNHI1aUo0WjVrTW5tdms2VWFyX1lxS3JxV21ldGI3Y1M0LVpyeFIwUTRvT3cwU3dqQm1TZm9pR3FOcGdaNk9PLW9VaWYwVHRHQ3lpakhKLVFnWXZKSzcyUVpEaHctenVHdWo2VXU5SUJldWNidUJqOENqMDFCTGt2YlFVR0t5T3V3YU5leTAtX0hiX1l6TGhXb2Y2RnhTREhQcTlMR1diZ2QtQzlkSHhkR3ZXNjJtNUJaZm5qdW5HUDg2bmEwZUc5UjZVR2E1ZHVR?oc=5</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>vinanet.vn</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>EPS miss</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>db01a046a3354e8ea09523383f8e8b1b</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>855b6643ce59f8ffa91338ca</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>0f01c7d4a0fd1ba5bfe6dd13</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.322</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPdEFVMDRjMEhVSUNmTkt4b212bkw3cmpRY0NOMG5HTjh6U0VWZnBXNmtnS1hkdjJURGVjUTBCNHI1aUo0WjVrTW5tdms2VWFyX1lxS3JxV21ldGI3Y1M0LVpyeFIwUTRvT3cwU3dqQm1TZm9pR3FOcGdaNk9PLW9VaWYwVHRHQ3lpakhKLVFnWXZKSzcyUVpEaHctenVHdWo2VXU5SUJldWNidUJqOENqMDFCTGt2YlFVR0t5T3V3YU5leTAtX0hiX1l6TGhXb2Y2RnhTREhQcTlMR1diZ2QtQzlkSHhkR3ZXNjJtNUJaZm5qdW5HUDg2bmEwZUc5UjZVR2E1ZHVR?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>vinanet.vn</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>EPS miss</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>855b6643ce59f8ffa91338ca</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>0f01c7d4a0fd1ba5bfe6dd13</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr"/>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="BC18" s="4" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF18" s="4" t="inlineStr"/>
-      <c r="BG18" s="4" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr"/>
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH18" s="4" t="inlineStr"/>
-      <c r="BI18" s="4" t="inlineStr"/>
-      <c r="BJ18" s="4" t="inlineStr"/>
-      <c r="BK18" s="4" t="inlineStr"/>
-      <c r="BL18" s="4" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4304,7 +4388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL8"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4906,12 +4990,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4921,7 +5005,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>EA devs feel "the threat of layoffs at all times," especially after Saudi Arabia acquisition: "It's hard to see how teams or games that underperform wouldn't be dissolved"</t>
+          <t>News - Lennar Mortgage data breach exposes personal information of more than 60,000 Texans</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -4932,7 +5016,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -4942,13 +5026,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -4958,7 +5046,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>'-0.945</t>
+          <t>'-0.926</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -4967,33 +5055,33 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>原始代號與公司名稱交叉核對</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPb1I2bm4zelljeVc1ckotVzMtTHhwQmlzLW53VGhPc041cGxvdGFEeVdaWExWMEw0MHJSYy1xQjRPUERMS0ZHRW5qN1NRVFJhdy02Y1R1TVRlWk43YW1QNFN6WWs2R25yc3pQcC1fRXZRWGVRbTRNMUZlT184OVpveUdZTFJTNjZ5Rk9NYWp2RzFOVHVNbVAw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdnZYOWhLcUdOcjdDXzFRenZYa1pfNy1ySDFHRlZ2OXJtSUFaMlo1bEZkS2M5QklBWURYNVRyZDJmZy1ETnViZm5reFR6WFJDT1A3TVVuMEhiUVlOeFA5TlFWLVV4RjcxVXRnamlsdFpxT19QWnJZSzRrOXdEQUQtTWlJOGQ1MGMxMGNvWFNzZlpYUWVSUVJON3UtOWRyeHVmRlNSMXVMLVBISDk4eEdWbGp6OWM3X0VD?oc=5</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>teiss</t>
         </is>
       </c>
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z3" s="4" t="inlineStr">
         <is>
-          <t>layoff；layoffs</t>
+          <t>data breach</t>
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr">
@@ -5001,15 +5089,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>a6033bd01de44f7d8ee262f2e080fada</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
-          <t>2df15df5265c5dd85d3cc96f</t>
+          <t>d6fe9154050795237fedcbbd</t>
         </is>
       </c>
       <c r="AD3" s="4" t="inlineStr">
         <is>
-          <t>f2d43c051b02f6d0e68cd5d6</t>
+          <t>98248d8bb5062e16bbdce959</t>
         </is>
       </c>
       <c r="AE3" s="4" t="inlineStr"/>
@@ -5022,7 +5114,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -5030,14 +5126,18 @@
       <c r="AT3" s="4" t="inlineStr"/>
       <c r="AU3" s="4" t="inlineStr"/>
       <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX3" s="4" t="inlineStr"/>
       <c r="AY3" s="4" t="inlineStr"/>
       <c r="AZ3" s="4" t="inlineStr"/>
       <c r="BA3" s="4" t="inlineStr"/>
       <c r="BB3" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="BC3" s="4" t="inlineStr">
@@ -5048,198 +5148,234 @@
       <c r="BD3" s="4" t="inlineStr"/>
       <c r="BE3" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG3" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH3" s="4" t="inlineStr"/>
       <c r="BI3" s="4" t="inlineStr"/>
       <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Lennar Corporation Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>News - Lennar Mortgage data breach exposes personal information of more than 60,000 Texans</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19T08:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Equifax Settlement Could Pay 4 Million Consumers Up to $280</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXNkT3lScldaMWk1bVNKX2xiaFhwNkxWYjd6ZG5kVWJMU3FIWDRlUTlEMFhPdnVhMk1MSkpudlRhaHVuRlZVNENOV2FFR3daMTdNcDFwSTBIbXZrZW0tMlVBcldXME5oQVhZRkc5Rk1Ub3hYZUl0c0pEeXZsTjN4dmJlRDFsbWdUU1hUbThVMERySzkyX3ZGc2wxUFlYSzjSAaQBQVVfeXFMTURITENfbWxtQlZycVVZNnhwLTVMM3hfZGR2VF9lLXZFMUVzQ0xtZXUtVnM2RWtBeUhxWFN6TlB6VUlCb2NPZXNtdldId3Zsb3BkWm1ZaVhXSjNESWdOaDduLTlZR1BZWGdteW9MQXlYYTVLaXZJanc4Rms4T2MxQVNVdDU5ZHh4MEpvMjJrSkw5WERjOFptR2tXbG9nTVlIa01rV1c?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>BadCredit.org</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>24d8747c26e34ed6881ad42db25cf75b</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>7d8a1737e4a003eb3c6d6ed7</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>fb248b9530e660b4d5037ed8</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.926</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdnZYOWhLcUdOcjdDXzFRenZYa1pfNy1ySDFHRlZ2OXJtSUFaMlo1bEZkS2M5QklBWURYNVRyZDJmZy1ETnViZm5reFR6WFJDT1A3TVVuMEhiUVlOeFA5TlFWLVV4RjcxVXRnamlsdFpxT19QWnJZSzRrOXdEQUQtTWlJOGQ1MGMxMGNvWFNzZlpYUWVSUVJON3UtOWRyeHVmRlNSMXVMLVBISDk4eEdWbGp6OWM3X0VD?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>teiss</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>d6fe9154050795237fedcbbd</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>98248d8bb5062e16bbdce959</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5254,22 +5390,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T08:00:00+08:00</t>
+          <t>2026-08-19T06:23:00+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Equifax Settlement Could Pay 4 Million Consumers Up to $280</t>
+          <t>Coinbase Must Face Investor Suit Over SEC, Bankruptcy Risks</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -5310,7 +5446,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>'-0.89</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -5324,18 +5460,18 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXNkT3lScldaMWk1bVNKX2xiaFhwNkxWYjd6ZG5kVWJMU3FIWDRlUTlEMFhPdnVhMk1MSkpudlRhaHVuRlZVNENOV2FFR3daMTdNcDFwSTBIbXZrZW0tMlVBcldXME5oQVhZRkc5Rk1Ub3hYZUl0c0pEeXZsTjN4dmJlRDFsbWdUU1hUbThVMERySzkyX3ZGc2wxUFlYSzjSAaQBQVVfeXFMTURITENfbWxtQlZycVVZNnhwLTVMM3hfZGR2VF9lLXZFMUVzQ0xtZXUtVnM2RWtBeUhxWFN6TlB6VUlCb2NPZXNtdldId3Zsb3BkWm1ZaVhXSjNESWdOaDduLTlZR1BZWGdteW9MQXlYYTVLaXZJanc4Rms4T2MxQVNVdDU5ZHh4MEpvMjJrSkw5WERjOFptR2tXbG9nTVlIa01rV1c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>BadCredit.org</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -5345,7 +5481,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>bankruptcy</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -5355,17 +5491,17 @@
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>24d8747c26e34ed6881ad42db25cf75b</t>
+          <t>011ea57ee19345e6a830245c47ce9892</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>7d8a1737e4a003eb3c6d6ed7</t>
+          <t>98220bbfad4ca2dced3d8acb</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>fb248b9530e660b4d5037ed8</t>
+          <t>8797dd1de30c63f33cb927ef</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -5390,18 +5526,14 @@
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
       <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW5" s="3" t="inlineStr"/>
       <c r="AX5" s="3" t="inlineStr"/>
       <c r="AY5" s="3" t="inlineStr"/>
       <c r="AZ5" s="3" t="inlineStr"/>
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -5412,23 +5544,19 @@
       <c r="BD5" s="3" t="inlineStr"/>
       <c r="BE5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr"/>
       <c r="BG5" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr">
         <is>
-          <t>Event_Code|事件中文</t>
+          <t>Event_Code|Level|事件中文</t>
         </is>
       </c>
       <c r="BJ5" s="3" t="inlineStr"/>
@@ -5444,561 +5572,197 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Eversource Energy</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19T06:42:47+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Eversource (ES) Financial Update: EPS Misses Its Estimate under the Current Snapshot; Session Reaction: The Stock Ends Up 0.43% at the Close - Quarterly Earnings Report</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AppLovin</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:19:00+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Apple Changes App Store Terms to Resolve E.U. Antitrust Dispute</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>'-0.39</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUDdna2V3bXFlOERIUnFkejQ5WkVBc2I3cVRoZXNGdWZDQnRMeUVEZ2x6VnVVbTJQenY4aDIwU0RLQ1JOMWVLazZmZ3N1MjVmLXFyc08xOWhBT0pLU1JDUzctczNpQmdkd1BuUHo0M1N3M3ZoNFktQmg4V2NOWjFwM2dxWngzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Barron's</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>c13f3ab3dc9a4caa9d5909c34cc0713d</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>723cdefc6cf396563b2b1ad0</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>ee5754561338bdfca7341bae</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.322</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPdEFVMDRjMEhVSUNmTkt4b212bkw3cmpRY0NOMG5HTjh6U0VWZnBXNmtnS1hkdjJURGVjUTBCNHI1aUo0WjVrTW5tdms2VWFyX1lxS3JxV21ldGI3Y1M0LVpyeFIwUTRvT3cwU3dqQm1TZm9pR3FOcGdaNk9PLW9VaWYwVHRHQ3lpakhKLVFnWXZKSzcyUVpEaHctenVHdWo2VXU5SUJldWNidUJqOENqMDFCTGt2YlFVR0t5T3V3YU5leTAtX0hiX1l6TGhXb2Y2RnhTREhQcTlMR1diZ2QtQzlkSHhkR3ZXNjJtNUJaZm5qdW5HUDg2bmEwZUc5UjZVR2E1ZHVR?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>vinanet.vn</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>EPS miss</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>855b6643ce59f8ffa91338ca</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>0f01c7d4a0fd1ba5bfe6dd13</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19T06:23:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase Must Face Investor Suit Over SEC, Bankruptcy Risks</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.89</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVHRnOW5OU3lLYVBhai16UzM2UVRDekZXZjRRcExuSlQzbDlzYXVYUEkwa3RxVUpLQ1UzYmVlTVdTbWhGcXJZaWFsMGJTYVFrX3dHRTJYQ2g4S3h0MmRVQkNMUEhibTJDNHI0Tk9wUWZ2TFd2NVdLMkRWUnlHNi1iaEVMbHN3Y2t6UEZ3RVR0bG9qUnRVbGZ6U0VIVklyRWRTcUtjZFQteVNrSHdpTkptMUpibnhWZU1FWHpN0gFyQVVfeXFMT2lSTmNyejU2QlBEcFdMc0VVVHVqZnh6WThlRWVJX285ckk4NXVIMHhoMy1xOVc1bUZONGNrWWhvX0t4SUI4SDhSN0xBeUtpUUZiWkdlYVowc042RW5CNWtSUHExdmh2eFgxNXlvc00xUk93?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>011ea57ee19345e6a830245c47ce9892</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>98220bbfad4ca2dced3d8acb</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>8797dd1de30c63f33cb927ef</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|Level|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD6" s="3" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>AppLovin</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19T02:19:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Apple Changes App Store Terms to Resolve E.U. Antitrust Dispute</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.39</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUDdna2V3bXFlOERIUnFkejQ5WkVBc2I3cVRoZXNGdWZDQnRMeUVEZ2x6VnVVbTJQenY4aDIwU0RLQ1JOMWVLazZmZ3N1MjVmLXFyc08xOWhBT0pLU1JDUzctczNpQmdkd1BuUHo0M1N3M3ZoNFktQmg4V2NOWjFwM2dxWngzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Barron's</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>c13f3ab3dc9a4caa9d5909c34cc0713d</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>723cdefc6cf396563b2b1ad0</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>ee5754561338bdfca7341bae</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL8" s="3" t="inlineStr">
+      <c r="BL6" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:43:17.016263+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL8"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6009,7 +5773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6400,186 +6164,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Wildfire updates: Level 1 evacuation order lifted for Mt. Hood corridor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.457</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNa2hlUWtBSWtrUk9JZEJOQXNHNTUyNVNjREVlaDNPZF9QYm5rSlk3TnZmci1pWTdwVlZhOHpwMkxzdDlHcGJxZWNHS3dYOGlFWExVNC1YYWxVSHFERmVsZThNODZYUlJ2UDNIeS1JT0VPVUoyYW5KNVJ4b3hJcXp5MWN3ckZHR2V5NFNFSERnUmhGaDdJOERGTEdaLXNlUzFHTVJleDNB?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>KPTV</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>4c6e285d6eb5907045fb1fbf</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>c5ebbbd5cab22dfbdfe435b3</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-19.xlsx
+++ b/news_daily/2026-08-19.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,21 +71,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4197,10 +4186,14 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -4363,7 +4356,11 @@
       </c>
       <c r="BG20" s="3" t="inlineStr"/>
       <c r="BH20" s="3" t="inlineStr"/>
-      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr">
+        <is>
+          <t>Company|Ticker</t>
+        </is>
+      </c>
       <c r="BJ20" s="3" t="inlineStr"/>
       <c r="BK20" s="3" t="inlineStr">
         <is>
@@ -5582,10 +5579,14 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -5748,7 +5749,11 @@
       </c>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Company|Ticker</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
       <c r="BK6" s="3" t="inlineStr">
         <is>

--- a/news_daily/2026-08-19.xlsx
+++ b/news_daily/2026-08-19.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
@@ -27,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,7 +66,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,13 +74,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -877,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -938,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -951,7 +966,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>b806d1e7ec55437f902896ca1817b0a4</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>727896ca29efd86f74911877</t>
@@ -972,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1016,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1257,28 +1292,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1318,7 +1357,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1331,7 +1370,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>48645b9d53d248eca5e62d2b4fabb6ec</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>54331ad265dda04ea7427b77</t>
@@ -1352,7 +1395,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1388,10 +1435,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1427,28 +1486,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1488,7 +1551,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1501,7 +1564,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>a1692ad86ee84aef93d96e9f4be5c9da</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>f8af972e521c7d4a0ed68f17</t>
@@ -1522,7 +1589,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1566,10 +1637,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,28 +2052,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2030,7 +2117,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2043,7 +2130,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>9b3d9e340f77413880e3a1910fd0f9cd</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>5eee5a2a361c9d51e21e894e</t>
@@ -2064,7 +2155,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2108,10 +2203,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2701,28 +2808,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2762,7 +2873,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2775,7 +2886,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>9ad57ee30170461aa36e0862dd4103f8</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>28f6f7190c2372d190484cd5</t>
@@ -2796,7 +2911,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2832,10 +2951,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2886,13 +3017,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2945,7 +3080,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>e4e7059e38ea453d93365ba852bef8b9</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>ab863246807dcbe3afd20f40</t>
@@ -2966,7 +3105,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3012,8 +3155,16 @@
       <c r="BH13" s="2" t="inlineStr"/>
       <c r="BI13" s="2" t="inlineStr"/>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3441,28 +3592,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3502,7 +3657,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3515,7 +3670,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>3fe8c309b5ad4562a9caf8b6c0340ac5</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>8b6ab96f86f9ea75584ec912</t>
@@ -3536,7 +3695,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3580,10 +3743,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">

--- a/news_daily/2026-08-19.xlsx
+++ b/news_daily/2026-08-19.xlsx
@@ -1890,17 +1890,17 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1908,7 +1908,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1951,7 +1955,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1964,7 +1968,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>55e2f31ad8044087ac730102917f5c0b</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>87d1f5a3a7d72746170a1984</t>
@@ -1985,7 +1993,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -2013,10 +2025,22 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2448,17 +2472,17 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2466,7 +2490,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2509,7 +2537,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2522,7 +2550,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>67ff401d95754f4aa538e546b85073cc</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>87d1f5a3a7d72746170a1984</t>
@@ -2543,7 +2575,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2571,10 +2607,22 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
